--- a/backend/data/financials_by_company/0180.HK.xlsx
+++ b/backend/data/financials_by_company/0180.HK.xlsx
@@ -4564,7 +4564,7 @@
         <v>36403000</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
         <v>0.69316</v>
